--- a/exports/VMM_full_report.xlsx
+++ b/exports/VMM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>18.28</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>102.74</v>
+        <v>100.69</v>
       </c>
       <c r="I2" t="n">
         <v>102.2711710579183</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.24</v>
+        <v>-6.15</v>
       </c>
       <c r="L2" t="n">
-        <v>5.86</v>
+        <v>6.56</v>
       </c>
       <c r="M2" t="n">
         <v>2.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>11.14</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>108.3</v>
+        <v>111.05</v>
       </c>
       <c r="I3" t="n">
         <v>108.9191235244728</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.56</v>
+        <v>-10.29</v>
       </c>
       <c r="L3" t="n">
-        <v>7.76</v>
+        <v>11.23</v>
       </c>
       <c r="M3" t="n">
         <v>1.83</v>
       </c>
       <c r="N3" t="n">
-        <v>3.96</v>
+        <v>5.54</v>
       </c>
       <c r="O3" t="n">
         <v>-2.55</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>111.2</v>
+        <v>107.25</v>
       </c>
       <c r="I4" t="n">
         <v>109.854644942253</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0.14</v>
+        <v>-3.42</v>
       </c>
       <c r="L4" t="n">
         <v>6.84</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>13.06</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>103.92</v>
+        <v>109.09</v>
       </c>
       <c r="I5" t="n">
         <v>106.0884672038077</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>-1.72</v>
       </c>
       <c r="L5" t="n">
         <v>4.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.59</v>
+        <v>2.47</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>5.39</v>
       </c>
       <c r="O5" t="n">
         <v>-3</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>7.95</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>105.81</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>102.2451932191311</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.01</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>3.93</v>
+        <v>11.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0.47</v>
+        <v>8.94</v>
       </c>
       <c r="N6" t="n">
         <v>3.39</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.02</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>107.61</v>
+        <v>109</v>
       </c>
       <c r="I7" t="n">
         <v>107.6785741432534</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.96</v>
+        <v>-9.35</v>
       </c>
       <c r="L7" t="n">
-        <v>9.15</v>
+        <v>11.54</v>
       </c>
       <c r="M7" t="n">
         <v>2.2</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>6.69</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>125</v>
+        <v>120.2</v>
       </c>
       <c r="I8" t="n">
         <v>122.0971486643864</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K8" t="n">
-        <v>14.68</v>
+        <v>10.28</v>
       </c>
       <c r="L8" t="n">
         <v>3.39</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2</v>
+        <v>7.61</v>
       </c>
       <c r="N8" t="n">
         <v>5.35</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.75</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45825.38541666666</v>
+        <v>45825.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>120.2</v>
+        <v>129.85</v>
       </c>
       <c r="I9" t="n">
         <v>128.3191117076864</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>8.07</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.67</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45866.38541666666</v>
+        <v>45866.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>137.44</v>
+        <v>132.9</v>
       </c>
       <c r="I10" t="n">
         <v>135.3808417272726</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K10" t="n">
-        <v>5.85</v>
+        <v>2.35</v>
       </c>
       <c r="L10" t="n">
         <v>7.96</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.84</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45873.38541666666</v>
+        <v>45873.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>141.09</v>
+        <v>141.6</v>
       </c>
       <c r="I11" t="n">
         <v>141.3736026615884</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.16</v>
+        <v>-6.55</v>
       </c>
       <c r="L11" t="n">
         <v>7.15</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.29</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>145.87</v>
+        <v>143.94</v>
       </c>
       <c r="I12" t="n">
         <v>145.3022847266296</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>52</v>
+        <v>52.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>3.02</v>
+        <v>1.65</v>
       </c>
       <c r="L12" t="n">
         <v>2.54</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.48</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>149.76</v>
+        <v>150.41</v>
       </c>
       <c r="I13" t="n">
         <v>150.0131846999899</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.04</v>
+        <v>-4.49</v>
       </c>
       <c r="L13" t="n">
         <v>5.72</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.58</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45964.38541666666</v>
+        <v>45964.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>142.91</v>
+        <v>142.17</v>
       </c>
       <c r="I14" t="n">
         <v>142.8029118561069</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.99</v>
+        <v>-5.48</v>
       </c>
       <c r="L14" t="n">
         <v>5.59</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.99</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46006.55208333334</v>
+        <v>46007.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>133.41</v>
+        <v>136.05</v>
       </c>
       <c r="I15" t="n">
         <v>135.4256253197362</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>6.16</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.6</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.58</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>134.16</v>
+        <v>130.03</v>
       </c>
       <c r="I16" t="n">
         <v>130.8863042738463</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.39</v>
+        <v>-4.42</v>
       </c>
       <c r="L16" t="n">
-        <v>2.86</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="O16" t="n">
         <v>1.9</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.76</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46076.55208333334</v>
+        <v>46077.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>120.3</v>
+        <v>124.02</v>
       </c>
       <c r="I17" t="n">
         <v>122.4353988237682</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K17" t="n">
-        <v>7.48</v>
+        <v>4.62</v>
       </c>
       <c r="L17" t="n">
         <v>3.36</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.29</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46080.38541666666</v>
+        <v>46080.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>118.83</v>
+        <v>117.86</v>
       </c>
       <c r="I18" t="n">
         <v>118.3358760469407</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.18</v>
+        <v>-4.97</v>
       </c>
       <c r="L18" t="n">
         <v>5.66</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.84</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>107.8</v>
+        <v>112.5</v>
       </c>
       <c r="I19" t="n">
         <v>108.0547251097005</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>8.539999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="L19" t="n">
         <v>0.96</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.36</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>119.55</v>
+        <v>115.67</v>
       </c>
       <c r="I20" t="n">
         <v>118.3994107225651</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K20" t="n">
-        <v>6.27</v>
+        <v>2.82</v>
       </c>
       <c r="L20" t="n">
         <v>6.2</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46255.55208333334</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>103.61</v>
+        <v>113.12</v>
       </c>
       <c r="I21" t="n">
         <v>107.3071363492534</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>99.16666666666667</v>
+        <v>102</v>
       </c>
       <c r="K21" t="n">
-        <v>10.43</v>
+        <v>2.2</v>
       </c>
       <c r="L21" t="n">
         <v>7.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.65</v>
+        <v>5.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.93</v>
+        <v>9.17</v>
       </c>
       <c r="O21" t="n">
         <v>-1.18</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>7.72</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>106.08</v>
+        <v>103.54</v>
       </c>
       <c r="I22" t="n">
         <v>105.6359913412548</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.22</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>6.99</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0.35</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.24</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>103.7</v>
+        <v>106.74</v>
       </c>
       <c r="I23" t="n">
         <v>104.8102707097602</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.15</v>
+        <v>-3.09</v>
       </c>
       <c r="L23" t="n">
-        <v>2.93</v>
+        <v>3.78</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
         <v>-2.26</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.54</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>103.45</v>
+        <v>101.62</v>
       </c>
       <c r="I24" t="n">
         <v>101.7791870400026</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.08</v>
+        <v>-4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>4.91</v>
       </c>
       <c r="M24" t="n">
         <v>0.03</v>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>2.79</v>
       </c>
       <c r="O24" t="n">
         <v>2.25</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1869,6 +2168,14 @@
       <c r="Q25" t="n">
         <v>40</v>
       </c>
+      <c r="R25" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2781,7 +3088,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.6</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="6">
@@ -2791,7 +3098,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -2801,7 +3108,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -2811,7 +3118,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -2821,7 +3128,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41.4</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="10">
@@ -2831,7 +3138,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="11">
@@ -2841,7 +3148,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -2851,7 +3158,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2861,7 +3168,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.9</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="14">
@@ -2871,7 +3178,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.55</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="15">
@@ -2881,7 +3188,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.24</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="16">
@@ -2891,7 +3198,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.89</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="17">
@@ -2901,7 +3208,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.68</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="18">
@@ -2911,7 +3218,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.5</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="19">
@@ -2921,7 +3228,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.9</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="20">
@@ -2931,7 +3238,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.59</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="21">
@@ -2941,7 +3248,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.15</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="22">
@@ -2951,7 +3258,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -2961,7 +3268,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2971,7 +3278,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.57</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="25">
@@ -2981,7 +3288,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.79</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="26">
@@ -2991,7 +3298,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="27">
@@ -3001,7 +3308,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.82</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="28">
@@ -3011,7 +3318,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
